--- a/products.xlsx
+++ b/products.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KD\Desktop\buying_shop_rebuild\buying_shop_rebuild\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KD\Desktop\SHOP_ONE_FOLDER_FINAL\SHOP_ONE_FOLDER_FINAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268EB2D6-C32C-484F-80D1-C2B78C21D64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D688FC-974B-412D-BD58-BFC794D141A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="1290" windowWidth="19425" windowHeight="14310" activeTab="1" xr2:uid="{65B9F4B2-DD0F-4070-B932-301A856A585D}"/>
+    <workbookView xWindow="7950" yWindow="345" windowWidth="19425" windowHeight="14310" xr2:uid="{65B9F4B2-DD0F-4070-B932-301A856A585D}"/>
   </bookViews>
   <sheets>
     <sheet name="가방" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2562" uniqueCount="526">
   <si>
     <t>id</t>
   </si>
@@ -1711,6 +1711,61 @@
   <si>
     <t>여성샌들</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>bag34</t>
+  </si>
+  <si>
+    <t>bag35</t>
+  </si>
+  <si>
+    <t>bag36</t>
+  </si>
+  <si>
+    <t>bag37</t>
+  </si>
+  <si>
+    <t>bag38</t>
+  </si>
+  <si>
+    <t>bag39</t>
+  </si>
+  <si>
+    <t>bag40</t>
+  </si>
+  <si>
+    <t>bag41</t>
+  </si>
+  <si>
+    <t>bag42</t>
+  </si>
+  <si>
+    <t>bag43</t>
+  </si>
+  <si>
+    <t>체크 체인 미니 숄더백</t>
+  </si>
+  <si>
+    <t>클래식한 체크 패턴에 골드 체인 디테일을 더한 미니 숄더백입니다. 작은 사이즈지만 포인트 아이템으로 활용하기 좋고, 데일리룩부터 여성스러운 코디까지 자연스럽게 매치됩니다. 체인 스트랩으로 고급스러운 분위기를 살렸으며 가볍게 들기 좋은 미니백 스타일입니다.</t>
+  </si>
+  <si>
+    <t>포인트 나일론 슬링백</t>
+  </si>
+  <si>
+    <t>깔끔한 블랙 컬러에 로고 밴드 포인트가 더해진 슬링백입니다. 가볍고 실용적인 나일론 소재감으로 데일리 착용에 좋으며, 허리백 또는 크로스백 스타일로 활용할 수 있습니다. 심플한 디자인에 포인트 스트랩 디테일이 더해져 캐주얼룩과 스트릿 코디에 자연스럽게 매치됩니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>체크 배색 로고 슬링백</t>
+  </si>
+  <si>
+    <t>클래식한 체크 패턴에 로고 밴드 포인트를 더한 슬링백입니다. 넉넉한 수납감과 가벼운 착용감으로 데일리백으로 활용하기 좋으며, 크로스백 또는 허리백 스타일로 자연스럽게 연출할 수 있습니다. 캐주얼룩과 스트릿 코디에 포인트 주기 좋은 아이템입니다.</t>
+  </si>
+  <si>
+    <t>심플 레더 미니 크로스백</t>
+  </si>
+  <si>
+    <t>깔끔한 블랙 컬러와 군더더기 없는 사각 쉐입이 돋보이는 미니 크로스백입니다. 전면 포켓 디테일로 실용성을 더했으며, 가벼운 사이즈감으로 데일리 착용에 좋습니다. 캐주얼룩부터 미니멀한 코디까지 자연스럽게 매치하기 좋은 아이템입니다.</t>
   </si>
 </sst>
 </file>
@@ -2718,7 +2773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A4DA53-A66D-4089-98E9-BD61446412BD}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
@@ -3940,7 +3995,7 @@
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="8" t="s">
         <v>461</v>
       </c>
       <c r="B27" t="s">
@@ -4122,7 +4177,7 @@
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="8" t="s">
         <v>465</v>
       </c>
       <c r="B31" t="s">
@@ -4175,9 +4230,15 @@
       <c r="C32" t="s">
         <v>16</v>
       </c>
+      <c r="D32" t="s">
+        <v>518</v>
+      </c>
       <c r="E32" t="str">
         <f t="shared" si="15"/>
-        <v>구매가 0원</v>
+        <v>구매가 648,000원</v>
+      </c>
+      <c r="G32" t="s">
+        <v>519</v>
       </c>
       <c r="H32" t="s">
         <v>466</v>
@@ -4186,18 +4247,24 @@
         <v>49</v>
       </c>
       <c r="K32" t="s">
-        <v>65</v>
+        <v>21</v>
+      </c>
+      <c r="L32">
+        <v>360</v>
       </c>
       <c r="M32" s="2">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>648000</v>
       </c>
       <c r="O32" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>0원</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+        <v>72000원</v>
+      </c>
+      <c r="P32">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>467</v>
       </c>
@@ -4207,9 +4274,15 @@
       <c r="C33" t="s">
         <v>16</v>
       </c>
+      <c r="D33" t="s">
+        <v>520</v>
+      </c>
       <c r="E33" t="str">
         <f t="shared" si="15"/>
-        <v>구매가 0원</v>
+        <v>구매가 810,000원</v>
+      </c>
+      <c r="G33" t="s">
+        <v>521</v>
       </c>
       <c r="H33" t="s">
         <v>467</v>
@@ -4218,18 +4291,24 @@
         <v>49</v>
       </c>
       <c r="K33" t="s">
-        <v>65</v>
+        <v>21</v>
+      </c>
+      <c r="L33">
+        <v>450</v>
       </c>
       <c r="M33" s="2">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>810000</v>
       </c>
       <c r="O33" s="6" t="str">
         <f t="shared" si="17"/>
-        <v>0원</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+        <v>90000원</v>
+      </c>
+      <c r="P33">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>468</v>
       </c>
@@ -4239,9 +4318,15 @@
       <c r="C34" t="s">
         <v>16</v>
       </c>
+      <c r="D34" t="s">
+        <v>522</v>
+      </c>
       <c r="E34" t="str">
         <f t="shared" si="15"/>
-        <v>구매가 0원</v>
+        <v>구매가 810,000원</v>
+      </c>
+      <c r="G34" t="s">
+        <v>523</v>
       </c>
       <c r="H34" t="s">
         <v>468</v>
@@ -4250,14 +4335,352 @@
         <v>49</v>
       </c>
       <c r="K34" t="s">
-        <v>65</v>
+        <v>21</v>
+      </c>
+      <c r="L34">
+        <v>450</v>
       </c>
       <c r="M34" s="2">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>810000</v>
       </c>
       <c r="O34" s="6" t="str">
         <f t="shared" si="17"/>
+        <v>90000원</v>
+      </c>
+      <c r="P34">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" t="s">
+        <v>524</v>
+      </c>
+      <c r="E35" t="str">
+        <f t="shared" ref="E35:E44" si="18">"구매가 "&amp;TEXT(M35,"#,##0")&amp;"원"</f>
+        <v>구매가 1,170,000원</v>
+      </c>
+      <c r="G35" t="s">
+        <v>525</v>
+      </c>
+      <c r="H35" t="s">
+        <v>508</v>
+      </c>
+      <c r="J35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K35" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35">
+        <v>650</v>
+      </c>
+      <c r="M35" s="2">
+        <f t="shared" ref="M35:M44" si="19">L35*200*9</f>
+        <v>1170000</v>
+      </c>
+      <c r="O35" s="6" t="str">
+        <f t="shared" ref="O35:O44" si="20">P35*200&amp;"원"</f>
+        <v>130000원</v>
+      </c>
+      <c r="P35">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>509</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="str">
+        <f t="shared" si="18"/>
+        <v>구매가 0원</v>
+      </c>
+      <c r="H36" t="s">
+        <v>509</v>
+      </c>
+      <c r="J36" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36" t="s">
+        <v>65</v>
+      </c>
+      <c r="M36" s="2">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="O36" s="6" t="str">
+        <f t="shared" si="20"/>
+        <v>0원</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>510</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" t="str">
+        <f t="shared" si="18"/>
+        <v>구매가 0원</v>
+      </c>
+      <c r="H37" t="s">
+        <v>510</v>
+      </c>
+      <c r="J37" t="s">
+        <v>49</v>
+      </c>
+      <c r="K37" t="s">
+        <v>65</v>
+      </c>
+      <c r="M37" s="2">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="O37" s="6" t="str">
+        <f t="shared" si="20"/>
+        <v>0원</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>511</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" t="str">
+        <f t="shared" si="18"/>
+        <v>구매가 0원</v>
+      </c>
+      <c r="H38" t="s">
+        <v>511</v>
+      </c>
+      <c r="J38" t="s">
+        <v>49</v>
+      </c>
+      <c r="K38" t="s">
+        <v>65</v>
+      </c>
+      <c r="M38" s="2">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="O38" s="6" t="str">
+        <f t="shared" si="20"/>
+        <v>0원</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>512</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" t="str">
+        <f t="shared" si="18"/>
+        <v>구매가 0원</v>
+      </c>
+      <c r="H39" t="s">
+        <v>512</v>
+      </c>
+      <c r="J39" t="s">
+        <v>49</v>
+      </c>
+      <c r="K39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39" s="2">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="O39" s="6" t="str">
+        <f t="shared" si="20"/>
+        <v>0원</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>513</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" t="str">
+        <f t="shared" si="18"/>
+        <v>구매가 0원</v>
+      </c>
+      <c r="H40" t="s">
+        <v>513</v>
+      </c>
+      <c r="J40" t="s">
+        <v>49</v>
+      </c>
+      <c r="K40" t="s">
+        <v>65</v>
+      </c>
+      <c r="M40" s="2">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="O40" s="6" t="str">
+        <f t="shared" si="20"/>
+        <v>0원</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>514</v>
+      </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" t="str">
+        <f t="shared" si="18"/>
+        <v>구매가 0원</v>
+      </c>
+      <c r="H41" t="s">
+        <v>514</v>
+      </c>
+      <c r="J41" t="s">
+        <v>49</v>
+      </c>
+      <c r="K41" t="s">
+        <v>65</v>
+      </c>
+      <c r="M41" s="2">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="O41" s="6" t="str">
+        <f t="shared" si="20"/>
+        <v>0원</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>515</v>
+      </c>
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" t="str">
+        <f t="shared" si="18"/>
+        <v>구매가 0원</v>
+      </c>
+      <c r="H42" t="s">
+        <v>515</v>
+      </c>
+      <c r="J42" t="s">
+        <v>49</v>
+      </c>
+      <c r="K42" t="s">
+        <v>65</v>
+      </c>
+      <c r="M42" s="2">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="O42" s="6" t="str">
+        <f t="shared" si="20"/>
+        <v>0원</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>516</v>
+      </c>
+      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" t="str">
+        <f t="shared" si="18"/>
+        <v>구매가 0원</v>
+      </c>
+      <c r="H43" t="s">
+        <v>516</v>
+      </c>
+      <c r="J43" t="s">
+        <v>49</v>
+      </c>
+      <c r="K43" t="s">
+        <v>65</v>
+      </c>
+      <c r="M43" s="2">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="O43" s="6" t="str">
+        <f t="shared" si="20"/>
+        <v>0원</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>517</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" t="str">
+        <f t="shared" si="18"/>
+        <v>구매가 0원</v>
+      </c>
+      <c r="H44" t="s">
+        <v>517</v>
+      </c>
+      <c r="J44" t="s">
+        <v>49</v>
+      </c>
+      <c r="K44" t="s">
+        <v>65</v>
+      </c>
+      <c r="M44" s="2">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="O44" s="6" t="str">
+        <f t="shared" si="20"/>
         <v>0원</v>
       </c>
     </row>
